--- a/engine/sc/qa/unit/data/xlsx/tablestyle-cellstyle-excluded-font.xlsx
+++ b/engine/sc/qa/unit/data/xlsx/tablestyle-cellstyle-excluded-font.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\balu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\bvarga\cp\online\engine\sc\qa\unit\data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E091B7BE-63A1-4554-9D64-771608FCF0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37D447E-11D6-461D-87FD-8EC4445545AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="2535" windowWidth="28800" windowHeight="15345" xr2:uid="{3F96529C-047B-44F3-973B-513522D9D35B}"/>
+    <workbookView xWindow="11595" yWindow="4125" windowWidth="18900" windowHeight="15345" xr2:uid="{3F96529C-047B-44F3-973B-513522D9D35B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -145,11 +145,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment textRotation="45"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -565,14 +568,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="4">
         <v>41558</v>
       </c>
       <c r="D4">
